--- a/ConsoleDeals_联盟链接表.xlsx
+++ b/ConsoleDeals_联盟链接表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LJH\Desktop\GameDealsSite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F84310B4-0569-4ECF-9998-9605310F2F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D31472D-07E4-4FB5-8135-986B1E061189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="216">
   <si>
     <t>联盟身份申请清单（先申请这几个，拿到联盟 ID 后再填游戏链接）</t>
   </si>
@@ -74,9 +74,6 @@
     <t>（填：已申请/已通过/待填ID）</t>
   </si>
   <si>
-    <t>先不急，等站内容厚了再申，避免薄内容被拒</t>
-  </si>
-  <si>
     <t>Green Man Gaming</t>
   </si>
   <si>
@@ -434,247 +431,256 @@
     <t>Indiana Jones and the Great Circle</t>
   </si>
   <si>
+    <t>Kingdom Come: Deliverance II</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/kingdom-come-deliverance-2</t>
+  </si>
+  <si>
+    <t>Kirby and the Forgotten Land</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/kirby-and-the-forgotten-land</t>
+  </si>
+  <si>
+    <t>Luigi's Mansion 3</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/luigis-mansion-3</t>
+  </si>
+  <si>
+    <t>Mario + Rabbids Sparks of Hope</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/mario-rabbids-sparks-of-hope</t>
+  </si>
+  <si>
+    <t>Marvel's Spider-Man 2</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/marvels-spider-man-2</t>
+  </si>
+  <si>
+    <t>Marvel's Spider-Man: Miles Morales</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/spider-man-miles-morales</t>
+  </si>
+  <si>
+    <t>Microsoft Flight Simulator</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/microsoft-flight-simulator</t>
+  </si>
+  <si>
+    <t>Monster Hunter Wilds</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/monster-hunter-wilds</t>
+  </si>
+  <si>
+    <t>Pikmin 4</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/pikmin-4</t>
+  </si>
+  <si>
+    <t>Ratchet &amp; Clank: Rift Apart</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/ratchet-and-clank-rift-apart</t>
+  </si>
+  <si>
+    <t>Red Dead Redemption 2</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/red-dead-redemption-2</t>
+  </si>
+  <si>
+    <t>Returnal</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/returnal</t>
+  </si>
+  <si>
+    <t>Rise of the Ronin</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/rise-of-the-ronin</t>
+  </si>
+  <si>
+    <t>Sea of Thieves</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/sea-of-thieves</t>
+  </si>
+  <si>
+    <t>Silent Hill 2 Remake</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/silent-hill-2-remake</t>
+  </si>
+  <si>
+    <t>Splatoon 3</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/splatoon-3</t>
+  </si>
+  <si>
+    <t>Star Wars Outlaws</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/star-wars-outlaws</t>
+  </si>
+  <si>
+    <t>Starfield</t>
+  </si>
+  <si>
+    <t>new-release, longtail</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/starfield</t>
+  </si>
+  <si>
+    <t>Stellar Blade</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/stellar-blade</t>
+  </si>
+  <si>
+    <t>The Last of Us Part II Remastered</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/the-last-of-us-part-ii-remastered</t>
+  </si>
+  <si>
+    <t>Xenoblade Chronicles 3</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/xenoblade-chronicles-3</t>
+  </si>
+  <si>
+    <t>Baldur's Gate 3</t>
+  </si>
+  <si>
+    <t>https://www.humblebundle.com/store/baldurs-gate-3</t>
+  </si>
+  <si>
+    <t>EA Sports FC 25</t>
+  </si>
+  <si>
+    <t>https://www.humblebundle.com/store/ea-sports-fc-25</t>
+  </si>
+  <si>
+    <t>Dying Light 2</t>
+  </si>
+  <si>
+    <t>https://www.fanatical.com/en/game/dying-light-2-stay-human</t>
+  </si>
+  <si>
+    <t>Hogwarts Legacy</t>
+  </si>
+  <si>
+    <t>https://www.fanatical.com/en/game/hogwarts-legacy</t>
+  </si>
+  <si>
+    <t>怎么用这张表</t>
+  </si>
+  <si>
+    <t>1) 先看【①联盟申请清单】 sheet，按里面网址去申请 4 个联盟账号。</t>
+  </si>
+  <si>
+    <t>2) 申请通过后，点开本表『当前商品链接（具体商品页）』列里那行对应的链接，在网站里找到这个商品，用你的联盟后台生成『带你追踪ID的推广链接』。</t>
+  </si>
+  <si>
+    <t>3) 回到【②游戏链接填报表】，在黄底列『【请回填】联盟推广链接』粘贴该链接；『回填状态』写『已填』。</t>
+  </si>
+  <si>
+    <t>4) 不用每个都填：先填你已通过的那几家网站对应的行即可，其余留空。</t>
+  </si>
+  <si>
+    <t>5) 填完后把整个 .xlsx 文件发回给我，我会把链接写进网站（更新 deals.json 的 storeUrl，并按需打开 config.ts 里对应网络的 enabled）。</t>
+  </si>
+  <si>
+    <t>关于『链接状态』列：</t>
+  </si>
+  <si>
+    <t>- 『已核实』：商品页 URL 已逐个联网核实，点开就是正确商品，直接用它生成联盟链接即可。</t>
+  </si>
+  <si>
+    <t>- 『推测·请确认』（橙色单元格）：GMG（被反爬保护，无法自动核实）和 Humble（官方商品页未搜到）这两家给的是『按命名规律推测的链接』，点开若是 404 或跳首页，请在该网站搜索框里搜游戏名，用你搜到的真实商品页生成联盟链接。</t>
+  </si>
+  <si>
+    <t>注意事项：</t>
+  </si>
+  <si>
+    <t>- 亚马逊：别手标价格、别用短链（bit.ly等）、文章页必须有 FTC 声明（网站模板已内置）。</t>
+  </si>
+  <si>
+    <t>- 一个游戏当前只挂了一个网站（见『网站/联盟』列），所以每行只需填那一家对应的推广链接。</t>
+  </si>
+  <si>
+    <t>- 若你某游戏想同时挂多家（比如 GMG + Humble），告诉我，我可以把那行拆成多行。</t>
+  </si>
+  <si>
+    <t>- 推广链接必须是『带你自己联盟ID』的完整链接，否则佣金不算你的。</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4wNJW7Q</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4q2cHLd</t>
+  </si>
+  <si>
+    <t>https://amzn.to/3RRsVdI</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4pZh1et</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4hjNmdI</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4fRrp33</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4bxrRCl</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4wUHyft</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4q4oucf</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4z1cmfZ</t>
+  </si>
+  <si>
+    <t>https://amzn.to/45Plnv6</t>
+  </si>
+  <si>
+    <t>https://amzn.to/45QLG45</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4xqwYwK</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4fUg8zb</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4xrrkud</t>
+  </si>
+  <si>
     <t>https://www.greenmangaming.com/games/indiana-jones-great-circle</t>
-  </si>
-  <si>
-    <t>Kingdom Come: Deliverance II</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/kingdom-come-deliverance-2</t>
-  </si>
-  <si>
-    <t>Kirby and the Forgotten Land</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/kirby-and-the-forgotten-land</t>
-  </si>
-  <si>
-    <t>Luigi's Mansion 3</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/luigis-mansion-3</t>
-  </si>
-  <si>
-    <t>Mario + Rabbids Sparks of Hope</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/mario-rabbids-sparks-of-hope</t>
-  </si>
-  <si>
-    <t>Marvel's Spider-Man 2</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/marvels-spider-man-2</t>
-  </si>
-  <si>
-    <t>Marvel's Spider-Man: Miles Morales</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/spider-man-miles-morales</t>
-  </si>
-  <si>
-    <t>Microsoft Flight Simulator</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/microsoft-flight-simulator</t>
-  </si>
-  <si>
-    <t>Monster Hunter Wilds</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/monster-hunter-wilds</t>
-  </si>
-  <si>
-    <t>Pikmin 4</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/pikmin-4</t>
-  </si>
-  <si>
-    <t>Ratchet &amp; Clank: Rift Apart</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/ratchet-and-clank-rift-apart</t>
-  </si>
-  <si>
-    <t>Red Dead Redemption 2</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/red-dead-redemption-2</t>
-  </si>
-  <si>
-    <t>Returnal</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/returnal</t>
-  </si>
-  <si>
-    <t>Rise of the Ronin</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/rise-of-the-ronin</t>
-  </si>
-  <si>
-    <t>Sea of Thieves</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/sea-of-thieves</t>
-  </si>
-  <si>
-    <t>Silent Hill 2 Remake</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/silent-hill-2-remake</t>
-  </si>
-  <si>
-    <t>Splatoon 3</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/splatoon-3</t>
-  </si>
-  <si>
-    <t>Star Wars Outlaws</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/star-wars-outlaws</t>
-  </si>
-  <si>
-    <t>Starfield</t>
-  </si>
-  <si>
-    <t>new-release, longtail</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/starfield</t>
-  </si>
-  <si>
-    <t>Stellar Blade</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/stellar-blade</t>
-  </si>
-  <si>
-    <t>The Last of Us Part II Remastered</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/the-last-of-us-part-ii-remastered</t>
-  </si>
-  <si>
-    <t>Xenoblade Chronicles 3</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/xenoblade-chronicles-3</t>
-  </si>
-  <si>
-    <t>Baldur's Gate 3</t>
-  </si>
-  <si>
-    <t>https://www.humblebundle.com/store/baldurs-gate-3</t>
-  </si>
-  <si>
-    <t>EA Sports FC 25</t>
-  </si>
-  <si>
-    <t>https://www.humblebundle.com/store/ea-sports-fc-25</t>
-  </si>
-  <si>
-    <t>Dying Light 2</t>
-  </si>
-  <si>
-    <t>https://www.fanatical.com/en/game/dying-light-2-stay-human</t>
-  </si>
-  <si>
-    <t>Hogwarts Legacy</t>
-  </si>
-  <si>
-    <t>https://www.fanatical.com/en/game/hogwarts-legacy</t>
-  </si>
-  <si>
-    <t>怎么用这张表</t>
-  </si>
-  <si>
-    <t>1) 先看【①联盟申请清单】 sheet，按里面网址去申请 4 个联盟账号。</t>
-  </si>
-  <si>
-    <t>2) 申请通过后，点开本表『当前商品链接（具体商品页）』列里那行对应的链接，在网站里找到这个商品，用你的联盟后台生成『带你追踪ID的推广链接』。</t>
-  </si>
-  <si>
-    <t>3) 回到【②游戏链接填报表】，在黄底列『【请回填】联盟推广链接』粘贴该链接；『回填状态』写『已填』。</t>
-  </si>
-  <si>
-    <t>4) 不用每个都填：先填你已通过的那几家网站对应的行即可，其余留空。</t>
-  </si>
-  <si>
-    <t>5) 填完后把整个 .xlsx 文件发回给我，我会把链接写进网站（更新 deals.json 的 storeUrl，并按需打开 config.ts 里对应网络的 enabled）。</t>
-  </si>
-  <si>
-    <t>关于『链接状态』列：</t>
-  </si>
-  <si>
-    <t>- 『已核实』：商品页 URL 已逐个联网核实，点开就是正确商品，直接用它生成联盟链接即可。</t>
-  </si>
-  <si>
-    <t>- 『推测·请确认』（橙色单元格）：GMG（被反爬保护，无法自动核实）和 Humble（官方商品页未搜到）这两家给的是『按命名规律推测的链接』，点开若是 404 或跳首页，请在该网站搜索框里搜游戏名，用你搜到的真实商品页生成联盟链接。</t>
-  </si>
-  <si>
-    <t>注意事项：</t>
-  </si>
-  <si>
-    <t>- 亚马逊：别手标价格、别用短链（bit.ly等）、文章页必须有 FTC 声明（网站模板已内置）。</t>
-  </si>
-  <si>
-    <t>- 一个游戏当前只挂了一个网站（见『网站/联盟』列），所以每行只需填那一家对应的推广链接。</t>
-  </si>
-  <si>
-    <t>- 若你某游戏想同时挂多家（比如 GMG + Humble），告诉我，我可以把那行拆成多行。</t>
-  </si>
-  <si>
-    <t>- 推广链接必须是『带你自己联盟ID』的完整链接，否则佣金不算你的。</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4wNJW7Q</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4q2cHLd</t>
-  </si>
-  <si>
-    <t>https://amzn.to/3RRsVdI</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4pZh1et</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4hjNmdI</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4fRrp33</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4bxrRCl</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4wUHyft</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4q4oucf</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4z1cmfZ</t>
-  </si>
-  <si>
-    <t>https://amzn.to/45Plnv6</t>
-  </si>
-  <si>
-    <t>https://amzn.to/45QLG45</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4xqwYwK</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4fUg8zb</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4xrrkud</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>已通过</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>已添加专属链接</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -694,6 +700,7 @@
       <sz val="14"/>
       <color rgb="FF1C2530"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -701,6 +708,7 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -782,11 +790,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1102,15 +1110,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
@@ -1152,79 +1160,79 @@
         <v>12</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>14</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="27" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="27" x14ac:dyDescent="0.15">
       <c r="A6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="27" x14ac:dyDescent="0.15">
       <c r="A7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1253,44 +1261,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
+      <c r="A1" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.15">
@@ -1301,22 +1309,22 @@
         <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>46</v>
-      </c>
       <c r="H4" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I4" s="4"/>
     </row>
@@ -1328,22 +1336,22 @@
         <v>8</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="G5" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I5" s="4"/>
     </row>
@@ -1355,22 +1363,22 @@
         <v>8</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="G6" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I6" s="4"/>
     </row>
@@ -1382,22 +1390,22 @@
         <v>8</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="G7" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I7" s="4"/>
     </row>
@@ -1409,22 +1417,22 @@
         <v>8</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="G8" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I8" s="4"/>
     </row>
@@ -1436,22 +1444,22 @@
         <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="G9" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I9" s="4"/>
     </row>
@@ -1463,22 +1471,22 @@
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="G10" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I10" s="4"/>
     </row>
@@ -1490,22 +1498,22 @@
         <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="G11" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>207</v>
+        <v>45</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>205</v>
       </c>
       <c r="I11" s="4"/>
     </row>
@@ -1517,22 +1525,22 @@
         <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="G12" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>208</v>
+        <v>45</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>206</v>
       </c>
       <c r="I12" s="4"/>
     </row>
@@ -1544,22 +1552,22 @@
         <v>8</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="G13" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>209</v>
+        <v>45</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>207</v>
       </c>
       <c r="I13" s="4"/>
     </row>
@@ -1571,22 +1579,22 @@
         <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="G14" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>210</v>
+        <v>45</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>208</v>
       </c>
       <c r="I14" s="4"/>
     </row>
@@ -1598,22 +1606,22 @@
         <v>8</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>73</v>
-      </c>
       <c r="G15" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>211</v>
+        <v>45</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>209</v>
       </c>
       <c r="I15" s="4"/>
     </row>
@@ -1625,22 +1633,22 @@
         <v>8</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="G16" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>212</v>
+        <v>45</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>210</v>
       </c>
       <c r="I16" s="4"/>
     </row>
@@ -1652,22 +1660,22 @@
         <v>8</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="G17" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>213</v>
+        <v>45</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>211</v>
       </c>
       <c r="I17" s="4"/>
     </row>
@@ -1679,22 +1687,22 @@
         <v>8</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="G18" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>214</v>
+        <v>45</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>212</v>
       </c>
       <c r="I18" s="4"/>
     </row>
@@ -1703,22 +1711,22 @@
         <v>16</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="E19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="G19" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="4"/>
@@ -1728,22 +1736,22 @@
         <v>17</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="E20" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="G20" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="4"/>
@@ -1753,22 +1761,22 @@
         <v>18</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="G21" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H21" s="5"/>
       <c r="I21" s="4"/>
@@ -1778,22 +1786,22 @@
         <v>19</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="G22" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="4"/>
@@ -1803,22 +1811,22 @@
         <v>20</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E23" s="3" t="s">
+      <c r="F23" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="G23" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H23" s="5"/>
       <c r="I23" s="4"/>
@@ -1828,22 +1836,22 @@
         <v>21</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="G24" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="4"/>
@@ -1853,22 +1861,22 @@
         <v>22</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E25" s="3" t="s">
+      <c r="F25" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="G25" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H25" s="5"/>
       <c r="I25" s="4"/>
@@ -1878,22 +1886,22 @@
         <v>23</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="G26" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="4"/>
@@ -1903,22 +1911,22 @@
         <v>24</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="G27" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H27" s="5"/>
       <c r="I27" s="4"/>
@@ -1928,22 +1936,22 @@
         <v>25</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C28" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E28" s="3" t="s">
+      <c r="F28" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F28" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="G28" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H28" s="5"/>
       <c r="I28" s="4"/>
@@ -1953,22 +1961,22 @@
         <v>26</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C29" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="G29" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H29" s="5"/>
       <c r="I29" s="4"/>
@@ -1978,22 +1986,22 @@
         <v>27</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C30" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D30" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="G30" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="4"/>
@@ -2003,22 +2011,22 @@
         <v>28</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D31" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="E31" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="G31" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="4"/>
@@ -2028,22 +2036,22 @@
         <v>29</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C32" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D32" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="G32" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="4"/>
@@ -2053,22 +2061,22 @@
         <v>30</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C33" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D33" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>116</v>
-      </c>
       <c r="G33" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H33" s="5"/>
       <c r="I33" s="4"/>
@@ -2078,22 +2086,22 @@
         <v>31</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C34" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D34" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="G34" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H34" s="5"/>
       <c r="I34" s="4"/>
@@ -2103,22 +2111,22 @@
         <v>32</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C35" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D35" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="G35" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H35" s="5"/>
       <c r="I35" s="4"/>
@@ -2128,22 +2136,22 @@
         <v>33</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C36" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="G36" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H36" s="5"/>
       <c r="I36" s="4"/>
@@ -2153,22 +2161,22 @@
         <v>34</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C37" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D37" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="G37" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H37" s="5"/>
       <c r="I37" s="4"/>
@@ -2178,22 +2186,22 @@
         <v>35</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C38" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D38" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>126</v>
-      </c>
       <c r="G38" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H38" s="5"/>
       <c r="I38" s="4"/>
@@ -2203,22 +2211,22 @@
         <v>36</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C39" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D39" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="G39" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H39" s="5"/>
       <c r="I39" s="4"/>
@@ -2228,22 +2236,22 @@
         <v>37</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C40" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D40" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>130</v>
-      </c>
       <c r="G40" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H40" s="5"/>
       <c r="I40" s="4"/>
@@ -2253,22 +2261,22 @@
         <v>38</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C41" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D41" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="G41" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H41" s="5"/>
       <c r="I41" s="4"/>
@@ -2278,22 +2286,22 @@
         <v>39</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>134</v>
+        <v>213</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H42" s="5"/>
       <c r="I42" s="4"/>
@@ -2303,22 +2311,22 @@
         <v>40</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H43" s="5"/>
       <c r="I43" s="4"/>
@@ -2328,22 +2336,22 @@
         <v>41</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H44" s="5"/>
       <c r="I44" s="4"/>
@@ -2353,22 +2361,22 @@
         <v>42</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H45" s="5"/>
       <c r="I45" s="4"/>
@@ -2378,22 +2386,22 @@
         <v>43</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H46" s="5"/>
       <c r="I46" s="4"/>
@@ -2403,22 +2411,22 @@
         <v>44</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H47" s="5"/>
       <c r="I47" s="4"/>
@@ -2428,22 +2436,22 @@
         <v>45</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H48" s="5"/>
       <c r="I48" s="4"/>
@@ -2453,22 +2461,22 @@
         <v>46</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H49" s="5"/>
       <c r="I49" s="4"/>
@@ -2478,22 +2486,22 @@
         <v>47</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H50" s="5"/>
       <c r="I50" s="4"/>
@@ -2503,22 +2511,22 @@
         <v>48</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H51" s="5"/>
       <c r="I51" s="4"/>
@@ -2528,22 +2536,22 @@
         <v>49</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H52" s="5"/>
       <c r="I52" s="4"/>
@@ -2553,22 +2561,22 @@
         <v>50</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H53" s="5"/>
       <c r="I53" s="4"/>
@@ -2578,22 +2586,22 @@
         <v>51</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H54" s="5"/>
       <c r="I54" s="4"/>
@@ -2603,22 +2611,22 @@
         <v>52</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H55" s="5"/>
       <c r="I55" s="4"/>
@@ -2628,22 +2636,22 @@
         <v>53</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H56" s="5"/>
       <c r="I56" s="4"/>
@@ -2653,22 +2661,22 @@
         <v>54</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H57" s="5"/>
       <c r="I57" s="4"/>
@@ -2678,22 +2686,22 @@
         <v>55</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D58" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E58" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="F58" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H58" s="5"/>
       <c r="I58" s="4"/>
@@ -2703,22 +2711,22 @@
         <v>56</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H59" s="5"/>
       <c r="I59" s="4"/>
@@ -2728,22 +2736,22 @@
         <v>57</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C60" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F60" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="D60" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="G60" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H60" s="5"/>
       <c r="I60" s="4"/>
@@ -2753,22 +2761,22 @@
         <v>58</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H61" s="5"/>
       <c r="I61" s="4"/>
@@ -2778,22 +2786,22 @@
         <v>59</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H62" s="5"/>
       <c r="I62" s="4"/>
@@ -2803,22 +2811,22 @@
         <v>60</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H63" s="5"/>
       <c r="I63" s="4"/>
@@ -2828,22 +2836,22 @@
         <v>61</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H64" s="5"/>
       <c r="I64" s="4"/>
@@ -2853,22 +2861,22 @@
         <v>62</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H65" s="5"/>
       <c r="I65" s="4"/>
@@ -2878,22 +2886,22 @@
         <v>63</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H66" s="5"/>
       <c r="I66" s="4"/>
@@ -2903,22 +2911,22 @@
         <v>64</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H67" s="5"/>
       <c r="I67" s="4"/>
@@ -2944,7 +2952,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.15">
@@ -2952,27 +2960,27 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="27" x14ac:dyDescent="0.15">
       <c r="A4" s="7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A5" s="7" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A6" s="7" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="27" x14ac:dyDescent="0.15">
       <c r="A7" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.15">
@@ -2980,17 +2988,17 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A9" s="7" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A10" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A11" s="7" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.15">
@@ -2998,27 +3006,27 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A13" s="7" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A14" s="7" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A15" s="7" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A16" s="7" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A17" s="7" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>

--- a/ConsoleDeals_联盟链接表.xlsx
+++ b/ConsoleDeals_联盟链接表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LJH\Desktop\GameDealsSite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D31472D-07E4-4FB5-8135-986B1E061189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B329E8B6-4483-45AB-85BA-68B56B3C302A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="219">
   <si>
     <t>联盟身份申请清单（先申请这几个，拿到联盟 ID 后再填游戏链接）</t>
   </si>
@@ -269,417 +269,463 @@
     <t>https://www.amazon.com/dp/B097B2YWFX</t>
   </si>
   <si>
+    <t>Cross-platform</t>
+  </si>
+  <si>
+    <t>推测·请确认</t>
+  </si>
+  <si>
+    <t>PlayStation 5</t>
+  </si>
+  <si>
+    <t>popular, new-release, weekly</t>
+  </si>
+  <si>
+    <t>popular, longtail, weekly</t>
+  </si>
+  <si>
+    <t>new-release, weekly</t>
+  </si>
+  <si>
+    <t>Xbox</t>
+  </si>
+  <si>
+    <t>Halo Infinite</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/halo-infinite</t>
+  </si>
+  <si>
+    <t>Helldivers 2</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/helldivers-2</t>
+  </si>
+  <si>
+    <t>Hi-Fi Rush</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/hi-fi-rush</t>
+  </si>
+  <si>
+    <t>Horizon Forbidden West</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/horizon-forbidden-west</t>
+  </si>
+  <si>
+    <t>Hyrule Warriors: Age of Calamity</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/hyrule-warriors-age-of-calamity</t>
+  </si>
+  <si>
+    <t>Indiana Jones and the Great Circle</t>
+  </si>
+  <si>
+    <t>Kingdom Come: Deliverance II</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/kingdom-come-deliverance-2</t>
+  </si>
+  <si>
+    <t>Kirby and the Forgotten Land</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/kirby-and-the-forgotten-land</t>
+  </si>
+  <si>
+    <t>Luigi's Mansion 3</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/luigis-mansion-3</t>
+  </si>
+  <si>
+    <t>Mario + Rabbids Sparks of Hope</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/mario-rabbids-sparks-of-hope</t>
+  </si>
+  <si>
+    <t>Marvel's Spider-Man 2</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/marvels-spider-man-2</t>
+  </si>
+  <si>
+    <t>Marvel's Spider-Man: Miles Morales</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/spider-man-miles-morales</t>
+  </si>
+  <si>
+    <t>Microsoft Flight Simulator</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/microsoft-flight-simulator</t>
+  </si>
+  <si>
+    <t>Monster Hunter Wilds</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/monster-hunter-wilds</t>
+  </si>
+  <si>
+    <t>Pikmin 4</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/pikmin-4</t>
+  </si>
+  <si>
+    <t>Ratchet &amp; Clank: Rift Apart</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/ratchet-and-clank-rift-apart</t>
+  </si>
+  <si>
+    <t>Red Dead Redemption 2</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/red-dead-redemption-2</t>
+  </si>
+  <si>
+    <t>Returnal</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/returnal</t>
+  </si>
+  <si>
+    <t>Rise of the Ronin</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/rise-of-the-ronin</t>
+  </si>
+  <si>
+    <t>Sea of Thieves</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/sea-of-thieves</t>
+  </si>
+  <si>
+    <t>Silent Hill 2 Remake</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/silent-hill-2-remake</t>
+  </si>
+  <si>
+    <t>Splatoon 3</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/splatoon-3</t>
+  </si>
+  <si>
+    <t>Star Wars Outlaws</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/star-wars-outlaws</t>
+  </si>
+  <si>
+    <t>Starfield</t>
+  </si>
+  <si>
+    <t>new-release, longtail</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/starfield</t>
+  </si>
+  <si>
+    <t>Stellar Blade</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/stellar-blade</t>
+  </si>
+  <si>
+    <t>The Last of Us Part II Remastered</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/the-last-of-us-part-ii-remastered</t>
+  </si>
+  <si>
+    <t>Xenoblade Chronicles 3</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/xenoblade-chronicles-3</t>
+  </si>
+  <si>
+    <t>Baldur's Gate 3</t>
+  </si>
+  <si>
+    <t>https://www.humblebundle.com/store/baldurs-gate-3</t>
+  </si>
+  <si>
+    <t>EA Sports FC 25</t>
+  </si>
+  <si>
+    <t>https://www.humblebundle.com/store/ea-sports-fc-25</t>
+  </si>
+  <si>
+    <t>Dying Light 2</t>
+  </si>
+  <si>
+    <t>https://www.fanatical.com/en/game/dying-light-2-stay-human</t>
+  </si>
+  <si>
+    <t>Hogwarts Legacy</t>
+  </si>
+  <si>
+    <t>https://www.fanatical.com/en/game/hogwarts-legacy</t>
+  </si>
+  <si>
+    <t>怎么用这张表</t>
+  </si>
+  <si>
+    <t>1) 先看【①联盟申请清单】 sheet，按里面网址去申请 4 个联盟账号。</t>
+  </si>
+  <si>
+    <t>2) 申请通过后，点开本表『当前商品链接（具体商品页）』列里那行对应的链接，在网站里找到这个商品，用你的联盟后台生成『带你追踪ID的推广链接』。</t>
+  </si>
+  <si>
+    <t>3) 回到【②游戏链接填报表】，在黄底列『【请回填】联盟推广链接』粘贴该链接；『回填状态』写『已填』。</t>
+  </si>
+  <si>
+    <t>4) 不用每个都填：先填你已通过的那几家网站对应的行即可，其余留空。</t>
+  </si>
+  <si>
+    <t>5) 填完后把整个 .xlsx 文件发回给我，我会把链接写进网站（更新 deals.json 的 storeUrl，并按需打开 config.ts 里对应网络的 enabled）。</t>
+  </si>
+  <si>
+    <t>关于『链接状态』列：</t>
+  </si>
+  <si>
+    <t>- 『已核实』：商品页 URL 已逐个联网核实，点开就是正确商品，直接用它生成联盟链接即可。</t>
+  </si>
+  <si>
+    <t>- 『推测·请确认』（橙色单元格）：GMG（被反爬保护，无法自动核实）和 Humble（官方商品页未搜到）这两家给的是『按命名规律推测的链接』，点开若是 404 或跳首页，请在该网站搜索框里搜游戏名，用你搜到的真实商品页生成联盟链接。</t>
+  </si>
+  <si>
+    <t>注意事项：</t>
+  </si>
+  <si>
+    <t>- 亚马逊：别手标价格、别用短链（bit.ly等）、文章页必须有 FTC 声明（网站模板已内置）。</t>
+  </si>
+  <si>
+    <t>- 一个游戏当前只挂了一个网站（见『网站/联盟』列），所以每行只需填那一家对应的推广链接。</t>
+  </si>
+  <si>
+    <t>- 若你某游戏想同时挂多家（比如 GMG + Humble），告诉我，我可以把那行拆成多行。</t>
+  </si>
+  <si>
+    <t>- 推广链接必须是『带你自己联盟ID』的完整链接，否则佣金不算你的。</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4wNJW7Q</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4q2cHLd</t>
+  </si>
+  <si>
+    <t>https://amzn.to/3RRsVdI</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4pZh1et</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4hjNmdI</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4fRrp33</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4bxrRCl</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4wUHyft</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4q4oucf</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4z1cmfZ</t>
+  </si>
+  <si>
+    <t>https://amzn.to/45Plnv6</t>
+  </si>
+  <si>
+    <t>https://amzn.to/45QLG45</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4xqwYwK</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4fUg8zb</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4xrrkud</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/indiana-jones-great-circle</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>已通过</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>已添加专属链接</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Humble Bundle</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cross-platform</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>Assassin's Creed Shadows</t>
-  </si>
-  <si>
-    <t>Cross-platform</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/assassins-creed-shadows</t>
-  </si>
-  <si>
-    <t>推测·请确认</t>
-  </si>
-  <si>
-    <t>Astro Bot</t>
-  </si>
-  <si>
-    <t>PlayStation 5</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/astro-bot</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/search?query=Assassin%27s%20Creed%20Shadows</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Green Man Gaming</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Avatar: Frontiers of Pandora</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/avatar-frontiers-of-pandora</t>
-  </si>
-  <si>
-    <t>Bayonetta 3</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/bayonetta-3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/avatar-frontiers-of-pandora-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/bayonetta-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Astor: Blade of the Monolith</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/astor-blade-of-the-monolith-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Bayonetta </t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Black Myth: Wukong</t>
-  </si>
-  <si>
-    <t>popular, new-release, weekly</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/black-myth-wukong</t>
-  </si>
-  <si>
-    <t>Call of Duty: Black Ops 6</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/call-of-duty-black-ops-6</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/black-myth-wukong-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/call-of-duty-modern-warfare-standard-edition-xbox/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CALL OF DUTY®: MODERN WARFARE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Cyberpunk 2077</t>
-  </si>
-  <si>
-    <t>popular, longtail, weekly</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/cyberpunk-2077</t>
-  </si>
-  <si>
-    <t>Demon's Souls</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/demons-souls</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/cyberpunk-2077-xbox/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demon Slayer -Kimetsu no Yaiba</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/demon-slayer-kimetsu-no-yaiba-the-hinokami-chronicles-2-deluxe-edition-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Elden Ring</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/elden-ring</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/elden-ring-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Final Fantasy VII Rebirth</t>
-  </si>
-  <si>
-    <t>new-release, weekly</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/final-fantasy-vii-rebirth</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/final-fantasy-vii-rebirth-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Final Fantasy XVI</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/final-fantasy-xvi</t>
-  </si>
-  <si>
-    <t>Fire Emblem Engage</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/fire-emblem-engage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/final-fantasy-xvi-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Star Fire: Eternal Cycle</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>steam</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/star-fire-eternal-cycle-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Forza Horizon 5</t>
-  </si>
-  <si>
-    <t>Xbox</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/forza-horizon-5</t>
-  </si>
-  <si>
-    <t>Gears 5</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/gears-5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/forza-horizon-5-xbox/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Metal Gear Solid V: The Definitive Experience</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/metal-gear-solid-v-the-definitive-experience/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Ghost of Tsushima</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/ghost-of-tsushima</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/ghost-of-tsushima-directors-cut-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>God of War Ragnarök</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/god-of-war-ragnarok</t>
-  </si>
-  <si>
-    <t>Gran Turismo 7</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/gran-turismo-7</t>
-  </si>
-  <si>
-    <t>Grand Theft Auto VI</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/grand-theft-auto-6</t>
-  </si>
-  <si>
-    <t>Halo Infinite</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/halo-infinite</t>
-  </si>
-  <si>
-    <t>Helldivers 2</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/helldivers-2</t>
-  </si>
-  <si>
-    <t>Hi-Fi Rush</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/hi-fi-rush</t>
-  </si>
-  <si>
-    <t>Horizon Forbidden West</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/horizon-forbidden-west</t>
-  </si>
-  <si>
-    <t>Hyrule Warriors: Age of Calamity</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/hyrule-warriors-age-of-calamity</t>
-  </si>
-  <si>
-    <t>Indiana Jones and the Great Circle</t>
-  </si>
-  <si>
-    <t>Kingdom Come: Deliverance II</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/kingdom-come-deliverance-2</t>
-  </si>
-  <si>
-    <t>Kirby and the Forgotten Land</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/kirby-and-the-forgotten-land</t>
-  </si>
-  <si>
-    <t>Luigi's Mansion 3</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/luigis-mansion-3</t>
-  </si>
-  <si>
-    <t>Mario + Rabbids Sparks of Hope</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/mario-rabbids-sparks-of-hope</t>
-  </si>
-  <si>
-    <t>Marvel's Spider-Man 2</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/marvels-spider-man-2</t>
-  </si>
-  <si>
-    <t>Marvel's Spider-Man: Miles Morales</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/spider-man-miles-morales</t>
-  </si>
-  <si>
-    <t>Microsoft Flight Simulator</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/microsoft-flight-simulator</t>
-  </si>
-  <si>
-    <t>Monster Hunter Wilds</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/monster-hunter-wilds</t>
-  </si>
-  <si>
-    <t>Pikmin 4</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/pikmin-4</t>
-  </si>
-  <si>
-    <t>Ratchet &amp; Clank: Rift Apart</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/ratchet-and-clank-rift-apart</t>
-  </si>
-  <si>
-    <t>Red Dead Redemption 2</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/red-dead-redemption-2</t>
-  </si>
-  <si>
-    <t>Returnal</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/returnal</t>
-  </si>
-  <si>
-    <t>Rise of the Ronin</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/rise-of-the-ronin</t>
-  </si>
-  <si>
-    <t>Sea of Thieves</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/sea-of-thieves</t>
-  </si>
-  <si>
-    <t>Silent Hill 2 Remake</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/silent-hill-2-remake</t>
-  </si>
-  <si>
-    <t>Splatoon 3</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/splatoon-3</t>
-  </si>
-  <si>
-    <t>Star Wars Outlaws</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/star-wars-outlaws</t>
-  </si>
-  <si>
-    <t>Starfield</t>
-  </si>
-  <si>
-    <t>new-release, longtail</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/starfield</t>
-  </si>
-  <si>
-    <t>Stellar Blade</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/stellar-blade</t>
-  </si>
-  <si>
-    <t>The Last of Us Part II Remastered</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/the-last-of-us-part-ii-remastered</t>
-  </si>
-  <si>
-    <t>Xenoblade Chronicles 3</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/xenoblade-chronicles-3</t>
-  </si>
-  <si>
-    <t>Baldur's Gate 3</t>
-  </si>
-  <si>
-    <t>https://www.humblebundle.com/store/baldurs-gate-3</t>
-  </si>
-  <si>
-    <t>EA Sports FC 25</t>
-  </si>
-  <si>
-    <t>https://www.humblebundle.com/store/ea-sports-fc-25</t>
-  </si>
-  <si>
-    <t>Dying Light 2</t>
-  </si>
-  <si>
-    <t>https://www.fanatical.com/en/game/dying-light-2-stay-human</t>
-  </si>
-  <si>
-    <t>Hogwarts Legacy</t>
-  </si>
-  <si>
-    <t>https://www.fanatical.com/en/game/hogwarts-legacy</t>
-  </si>
-  <si>
-    <t>怎么用这张表</t>
-  </si>
-  <si>
-    <t>1) 先看【①联盟申请清单】 sheet，按里面网址去申请 4 个联盟账号。</t>
-  </si>
-  <si>
-    <t>2) 申请通过后，点开本表『当前商品链接（具体商品页）』列里那行对应的链接，在网站里找到这个商品，用你的联盟后台生成『带你追踪ID的推广链接』。</t>
-  </si>
-  <si>
-    <t>3) 回到【②游戏链接填报表】，在黄底列『【请回填】联盟推广链接』粘贴该链接；『回填状态』写『已填』。</t>
-  </si>
-  <si>
-    <t>4) 不用每个都填：先填你已通过的那几家网站对应的行即可，其余留空。</t>
-  </si>
-  <si>
-    <t>5) 填完后把整个 .xlsx 文件发回给我，我会把链接写进网站（更新 deals.json 的 storeUrl，并按需打开 config.ts 里对应网络的 enabled）。</t>
-  </si>
-  <si>
-    <t>关于『链接状态』列：</t>
-  </si>
-  <si>
-    <t>- 『已核实』：商品页 URL 已逐个联网核实，点开就是正确商品，直接用它生成联盟链接即可。</t>
-  </si>
-  <si>
-    <t>- 『推测·请确认』（橙色单元格）：GMG（被反爬保护，无法自动核实）和 Humble（官方商品页未搜到）这两家给的是『按命名规律推测的链接』，点开若是 404 或跳首页，请在该网站搜索框里搜游戏名，用你搜到的真实商品页生成联盟链接。</t>
-  </si>
-  <si>
-    <t>注意事项：</t>
-  </si>
-  <si>
-    <t>- 亚马逊：别手标价格、别用短链（bit.ly等）、文章页必须有 FTC 声明（网站模板已内置）。</t>
-  </si>
-  <si>
-    <t>- 一个游戏当前只挂了一个网站（见『网站/联盟』列），所以每行只需填那一家对应的推广链接。</t>
-  </si>
-  <si>
-    <t>- 若你某游戏想同时挂多家（比如 GMG + Humble），告诉我，我可以把那行拆成多行。</t>
-  </si>
-  <si>
-    <t>- 推广链接必须是『带你自己联盟ID』的完整链接，否则佣金不算你的。</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4wNJW7Q</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4q2cHLd</t>
-  </si>
-  <si>
-    <t>https://amzn.to/3RRsVdI</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4pZh1et</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4hjNmdI</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4fRrp33</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4bxrRCl</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4wUHyft</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4q4oucf</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4z1cmfZ</t>
-  </si>
-  <si>
-    <t>https://amzn.to/45Plnv6</t>
-  </si>
-  <si>
-    <t>https://amzn.to/45QLG45</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4xqwYwK</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4fUg8zb</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4xrrkud</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/indiana-jones-great-circle</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>已通过</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>已添加专属链接</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/god-of-war-ragnarok-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Witchspire</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/witchspire-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Grand Theft Auto V Enhanced &amp; Great White Shark Card Bundle</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1160,10 +1206,10 @@
         <v>12</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>214</v>
+        <v>178</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>215</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="27" x14ac:dyDescent="0.15">
@@ -1191,7 +1237,7 @@
     </row>
     <row r="6" spans="1:7" ht="27" x14ac:dyDescent="0.15">
       <c r="A6" s="3" t="s">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>21</v>
@@ -1324,7 +1370,7 @@
         <v>45</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>198</v>
+        <v>162</v>
       </c>
       <c r="I4" s="4"/>
     </row>
@@ -1351,7 +1397,7 @@
         <v>45</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>199</v>
+        <v>163</v>
       </c>
       <c r="I5" s="4"/>
     </row>
@@ -1378,7 +1424,7 @@
         <v>45</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>200</v>
+        <v>164</v>
       </c>
       <c r="I6" s="4"/>
     </row>
@@ -1405,7 +1451,7 @@
         <v>45</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
       <c r="I7" s="4"/>
     </row>
@@ -1432,7 +1478,7 @@
         <v>45</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>202</v>
+        <v>166</v>
       </c>
       <c r="I8" s="4"/>
     </row>
@@ -1459,7 +1505,7 @@
         <v>45</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>203</v>
+        <v>167</v>
       </c>
       <c r="I9" s="4"/>
     </row>
@@ -1486,7 +1532,7 @@
         <v>45</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>204</v>
+        <v>168</v>
       </c>
       <c r="I10" s="4"/>
     </row>
@@ -1513,7 +1559,7 @@
         <v>45</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="I11" s="4"/>
     </row>
@@ -1540,7 +1586,7 @@
         <v>45</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>206</v>
+        <v>170</v>
       </c>
       <c r="I12" s="4"/>
     </row>
@@ -1567,7 +1613,7 @@
         <v>45</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>207</v>
+        <v>171</v>
       </c>
       <c r="I13" s="4"/>
     </row>
@@ -1594,7 +1640,7 @@
         <v>45</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>208</v>
+        <v>172</v>
       </c>
       <c r="I14" s="4"/>
     </row>
@@ -1621,7 +1667,7 @@
         <v>45</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>209</v>
+        <v>173</v>
       </c>
       <c r="I15" s="4"/>
     </row>
@@ -1648,7 +1694,7 @@
         <v>45</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="I16" s="4"/>
     </row>
@@ -1675,7 +1721,7 @@
         <v>45</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>211</v>
+        <v>175</v>
       </c>
       <c r="I17" s="4"/>
     </row>
@@ -1702,7 +1748,7 @@
         <v>45</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>212</v>
+        <v>176</v>
       </c>
       <c r="I18" s="4"/>
     </row>
@@ -1711,27 +1757,27 @@
         <v>16</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>14</v>
+        <v>184</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>79</v>
+        <v>182</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>80</v>
+        <v>181</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F19" s="3" t="s">
-        <v>81</v>
-      </c>
+      <c r="F19" s="3"/>
       <c r="G19" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H19" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>183</v>
+      </c>
       <c r="I19" s="4"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A20" s="4">
         <v>17</v>
       </c>
@@ -1739,21 +1785,21 @@
         <v>14</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>83</v>
+        <v>188</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>85</v>
-      </c>
+      <c r="F20" s="3"/>
       <c r="G20" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H20" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>189</v>
+      </c>
       <c r="I20" s="4"/>
     </row>
     <row r="21" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -1764,24 +1810,24 @@
         <v>14</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>86</v>
+        <v>185</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>87</v>
-      </c>
+      <c r="F21" s="3"/>
       <c r="G21" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H21" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>186</v>
+      </c>
       <c r="I21" s="4"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A22" s="4">
         <v>19</v>
       </c>
@@ -1789,7 +1835,7 @@
         <v>14</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>88</v>
+        <v>190</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>42</v>
@@ -1797,13 +1843,13 @@
       <c r="E22" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>89</v>
-      </c>
+      <c r="F22" s="3"/>
       <c r="G22" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H22" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>187</v>
+      </c>
       <c r="I22" s="4"/>
     </row>
     <row r="23" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -1814,21 +1860,21 @@
         <v>14</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>92</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="F23" s="3"/>
       <c r="G23" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H23" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>192</v>
+      </c>
       <c r="I23" s="4"/>
     </row>
     <row r="24" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -1839,21 +1885,21 @@
         <v>14</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>93</v>
+        <v>194</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>94</v>
-      </c>
+      <c r="F24" s="3"/>
       <c r="G24" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H24" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>193</v>
+      </c>
       <c r="I24" s="4"/>
     </row>
     <row r="25" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -1864,49 +1910,47 @@
         <v>14</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>95</v>
+        <v>195</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>97</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="F25" s="3"/>
       <c r="G25" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H25" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>196</v>
+      </c>
       <c r="I25" s="4"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A26" s="4">
         <v>23</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>14</v>
+        <v>184</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>84</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="D26" s="4"/>
       <c r="E26" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>99</v>
-      </c>
+      <c r="F26" s="3"/>
       <c r="G26" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H26" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>198</v>
+      </c>
       <c r="I26" s="4"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A27" s="4">
         <v>24</v>
       </c>
@@ -1914,21 +1958,21 @@
         <v>14</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>100</v>
+        <v>199</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>101</v>
-      </c>
+      <c r="F27" s="3"/>
       <c r="G27" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H27" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>200</v>
+      </c>
       <c r="I27" s="4"/>
     </row>
     <row r="28" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -1939,21 +1983,21 @@
         <v>14</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>102</v>
+        <v>201</v>
       </c>
       <c r="D28" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>104</v>
-      </c>
+      <c r="F28" s="3"/>
       <c r="G28" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H28" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>202</v>
+      </c>
       <c r="I28" s="4"/>
     </row>
     <row r="29" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -1964,21 +2008,21 @@
         <v>14</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>105</v>
+        <v>203</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F29" s="3" t="s">
-        <v>106</v>
-      </c>
+      <c r="F29" s="3"/>
       <c r="G29" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H29" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>204</v>
+      </c>
       <c r="I29" s="4"/>
     </row>
     <row r="30" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -1989,21 +2033,19 @@
         <v>14</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>107</v>
+        <v>205</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>108</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
       <c r="G30" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H30" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>207</v>
+      </c>
       <c r="I30" s="4"/>
     </row>
     <row r="31" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -2014,24 +2056,24 @@
         <v>14</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>109</v>
+        <v>208</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F31" s="3" t="s">
-        <v>111</v>
-      </c>
+      <c r="F31" s="3"/>
       <c r="G31" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H31" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>209</v>
+      </c>
       <c r="I31" s="4"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A32" s="4">
         <v>29</v>
       </c>
@@ -2039,21 +2081,19 @@
         <v>14</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>112</v>
+        <v>210</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>113</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
       <c r="G32" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H32" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>211</v>
+      </c>
       <c r="I32" s="4"/>
     </row>
     <row r="33" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -2064,21 +2104,21 @@
         <v>14</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>114</v>
+        <v>212</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>115</v>
-      </c>
+      <c r="F33" s="3"/>
       <c r="G33" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H33" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>213</v>
+      </c>
       <c r="I33" s="4"/>
     </row>
     <row r="34" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -2089,21 +2129,21 @@
         <v>14</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>116</v>
+        <v>214</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F34" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="F34" s="3"/>
       <c r="G34" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H34" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>215</v>
+      </c>
       <c r="I34" s="4"/>
     </row>
     <row r="35" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -2114,21 +2154,17 @@
         <v>14</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>119</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="D35" s="4"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
       <c r="G35" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H35" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>217</v>
+      </c>
       <c r="I35" s="4"/>
     </row>
     <row r="36" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -2139,19 +2175,13 @@
         <v>14</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>121</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
       <c r="G36" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H36" s="5"/>
       <c r="I36" s="4"/>
@@ -2164,19 +2194,19 @@
         <v>14</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H37" s="5"/>
       <c r="I37" s="4"/>
@@ -2189,19 +2219,19 @@
         <v>14</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H38" s="5"/>
       <c r="I38" s="4"/>
@@ -2214,19 +2244,19 @@
         <v>14</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>57</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H39" s="5"/>
       <c r="I39" s="4"/>
@@ -2239,19 +2269,19 @@
         <v>14</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>51</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H40" s="5"/>
       <c r="I40" s="4"/>
@@ -2264,7 +2294,7 @@
         <v>14</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>42</v>
@@ -2273,10 +2303,10 @@
         <v>57</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>131</v>
+        <v>95</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H41" s="5"/>
       <c r="I41" s="4"/>
@@ -2289,19 +2319,19 @@
         <v>14</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>132</v>
+        <v>96</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>213</v>
+        <v>177</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H42" s="5"/>
       <c r="I42" s="4"/>
@@ -2314,19 +2344,19 @@
         <v>14</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>133</v>
+        <v>97</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H43" s="5"/>
       <c r="I43" s="4"/>
@@ -2339,7 +2369,7 @@
         <v>14</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>42</v>
@@ -2348,10 +2378,10 @@
         <v>57</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H44" s="5"/>
       <c r="I44" s="4"/>
@@ -2364,7 +2394,7 @@
         <v>14</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>137</v>
+        <v>101</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>42</v>
@@ -2373,10 +2403,10 @@
         <v>57</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H45" s="5"/>
       <c r="I45" s="4"/>
@@ -2389,7 +2419,7 @@
         <v>14</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>42</v>
@@ -2398,10 +2428,10 @@
         <v>57</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>140</v>
+        <v>104</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H46" s="5"/>
       <c r="I46" s="4"/>
@@ -2414,19 +2444,19 @@
         <v>14</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>51</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>142</v>
+        <v>106</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H47" s="5"/>
       <c r="I47" s="4"/>
@@ -2439,19 +2469,19 @@
         <v>14</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>57</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H48" s="5"/>
       <c r="I48" s="4"/>
@@ -2464,19 +2494,19 @@
         <v>14</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>145</v>
+        <v>109</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>57</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>146</v>
+        <v>110</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H49" s="5"/>
       <c r="I49" s="4"/>
@@ -2489,19 +2519,19 @@
         <v>14</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H50" s="5"/>
       <c r="I50" s="4"/>
@@ -2514,7 +2544,7 @@
         <v>14</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>149</v>
+        <v>113</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>42</v>
@@ -2523,10 +2553,10 @@
         <v>57</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>150</v>
+        <v>114</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H51" s="5"/>
       <c r="I51" s="4"/>
@@ -2539,19 +2569,19 @@
         <v>14</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>151</v>
+        <v>115</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H52" s="5"/>
       <c r="I52" s="4"/>
@@ -2564,19 +2594,19 @@
         <v>14</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>154</v>
+        <v>118</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H53" s="5"/>
       <c r="I53" s="4"/>
@@ -2589,19 +2619,19 @@
         <v>14</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>155</v>
+        <v>119</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>57</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>156</v>
+        <v>120</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H54" s="5"/>
       <c r="I54" s="4"/>
@@ -2614,19 +2644,19 @@
         <v>14</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>158</v>
+        <v>122</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H55" s="5"/>
       <c r="I55" s="4"/>
@@ -2639,19 +2669,19 @@
         <v>14</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>159</v>
+        <v>123</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>57</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H56" s="5"/>
       <c r="I56" s="4"/>
@@ -2664,19 +2694,19 @@
         <v>14</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>161</v>
+        <v>125</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>162</v>
+        <v>126</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H57" s="5"/>
       <c r="I57" s="4"/>
@@ -2689,7 +2719,7 @@
         <v>14</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>163</v>
+        <v>127</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>42</v>
@@ -2698,10 +2728,10 @@
         <v>43</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H58" s="5"/>
       <c r="I58" s="4"/>
@@ -2714,19 +2744,19 @@
         <v>14</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H59" s="5"/>
       <c r="I59" s="4"/>
@@ -2739,19 +2769,19 @@
         <v>14</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>168</v>
+        <v>132</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>169</v>
+        <v>133</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H60" s="5"/>
       <c r="I60" s="4"/>
@@ -2764,19 +2794,19 @@
         <v>14</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>170</v>
+        <v>134</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>171</v>
+        <v>135</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H61" s="5"/>
       <c r="I61" s="4"/>
@@ -2789,19 +2819,19 @@
         <v>14</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>172</v>
+        <v>136</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>173</v>
+        <v>137</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H62" s="5"/>
       <c r="I62" s="4"/>
@@ -2814,7 +2844,7 @@
         <v>14</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>174</v>
+        <v>138</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>42</v>
@@ -2823,10 +2853,10 @@
         <v>57</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>175</v>
+        <v>139</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H63" s="5"/>
       <c r="I63" s="4"/>
@@ -2839,19 +2869,19 @@
         <v>20</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>176</v>
+        <v>140</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>51</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>177</v>
+        <v>141</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H64" s="5"/>
       <c r="I64" s="4"/>
@@ -2864,19 +2894,19 @@
         <v>20</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>178</v>
+        <v>142</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>51</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>179</v>
+        <v>143</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H65" s="5"/>
       <c r="I65" s="4"/>
@@ -2889,16 +2919,16 @@
         <v>26</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>180</v>
+        <v>144</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>57</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="G66" s="4" t="s">
         <v>45</v>
@@ -2914,16 +2944,16 @@
         <v>26</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>51</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="G67" s="4" t="s">
         <v>45</v>
@@ -2937,8 +2967,11 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="H19" r:id="rId1" xr:uid="{02F8BF2D-5194-4074-AB9D-0555A539C933}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2952,7 +2985,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>184</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.15">
@@ -2960,27 +2993,27 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" s="7" t="s">
-        <v>185</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="27" x14ac:dyDescent="0.15">
       <c r="A4" s="7" t="s">
-        <v>186</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A5" s="7" t="s">
-        <v>187</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A6" s="7" t="s">
-        <v>188</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="27" x14ac:dyDescent="0.15">
       <c r="A7" s="7" t="s">
-        <v>189</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.15">
@@ -2988,17 +3021,17 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A9" s="7" t="s">
-        <v>190</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A10" s="7" t="s">
-        <v>191</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A11" s="7" t="s">
-        <v>192</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.15">
@@ -3006,27 +3039,27 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A13" s="7" t="s">
-        <v>193</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A14" s="7" t="s">
-        <v>194</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A15" s="7" t="s">
-        <v>195</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A16" s="7" t="s">
-        <v>196</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A17" s="7" t="s">
-        <v>197</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/ConsoleDeals_联盟链接表.xlsx
+++ b/ConsoleDeals_联盟链接表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LJH\Desktop\GameDealsSite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B329E8B6-4483-45AB-85BA-68B56B3C302A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{189007FD-D519-4070-A8C9-AC30862141C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="231">
   <si>
     <t>联盟身份申请清单（先申请这几个，拿到联盟 ID 后再填游戏链接）</t>
   </si>
@@ -290,442 +290,537 @@
     <t>Xbox</t>
   </si>
   <si>
+    <t>Returnal</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/returnal</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/rise-of-the-ronin</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/sea-of-thieves</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/star-wars-outlaws</t>
+  </si>
+  <si>
+    <t>new-release, longtail</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/starfield</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/stellar-blade</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/the-last-of-us-part-ii-remastered</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/xenoblade-chronicles-3</t>
+  </si>
+  <si>
+    <t>https://www.humblebundle.com/store/baldurs-gate-3</t>
+  </si>
+  <si>
+    <t>https://www.humblebundle.com/store/ea-sports-fc-25</t>
+  </si>
+  <si>
+    <t>Hogwarts Legacy</t>
+  </si>
+  <si>
+    <t>https://www.fanatical.com/en/game/hogwarts-legacy</t>
+  </si>
+  <si>
+    <t>怎么用这张表</t>
+  </si>
+  <si>
+    <t>1) 先看【①联盟申请清单】 sheet，按里面网址去申请 4 个联盟账号。</t>
+  </si>
+  <si>
+    <t>2) 申请通过后，点开本表『当前商品链接（具体商品页）』列里那行对应的链接，在网站里找到这个商品，用你的联盟后台生成『带你追踪ID的推广链接』。</t>
+  </si>
+  <si>
+    <t>3) 回到【②游戏链接填报表】，在黄底列『【请回填】联盟推广链接』粘贴该链接；『回填状态』写『已填』。</t>
+  </si>
+  <si>
+    <t>4) 不用每个都填：先填你已通过的那几家网站对应的行即可，其余留空。</t>
+  </si>
+  <si>
+    <t>5) 填完后把整个 .xlsx 文件发回给我，我会把链接写进网站（更新 deals.json 的 storeUrl，并按需打开 config.ts 里对应网络的 enabled）。</t>
+  </si>
+  <si>
+    <t>关于『链接状态』列：</t>
+  </si>
+  <si>
+    <t>- 『已核实』：商品页 URL 已逐个联网核实，点开就是正确商品，直接用它生成联盟链接即可。</t>
+  </si>
+  <si>
+    <t>- 『推测·请确认』（橙色单元格）：GMG（被反爬保护，无法自动核实）和 Humble（官方商品页未搜到）这两家给的是『按命名规律推测的链接』，点开若是 404 或跳首页，请在该网站搜索框里搜游戏名，用你搜到的真实商品页生成联盟链接。</t>
+  </si>
+  <si>
+    <t>注意事项：</t>
+  </si>
+  <si>
+    <t>- 亚马逊：别手标价格、别用短链（bit.ly等）、文章页必须有 FTC 声明（网站模板已内置）。</t>
+  </si>
+  <si>
+    <t>- 一个游戏当前只挂了一个网站（见『网站/联盟』列），所以每行只需填那一家对应的推广链接。</t>
+  </si>
+  <si>
+    <t>- 若你某游戏想同时挂多家（比如 GMG + Humble），告诉我，我可以把那行拆成多行。</t>
+  </si>
+  <si>
+    <t>- 推广链接必须是『带你自己联盟ID』的完整链接，否则佣金不算你的。</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4wNJW7Q</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4q2cHLd</t>
+  </si>
+  <si>
+    <t>https://amzn.to/3RRsVdI</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4pZh1et</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4hjNmdI</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4fRrp33</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4bxrRCl</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4wUHyft</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4q4oucf</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4z1cmfZ</t>
+  </si>
+  <si>
+    <t>https://amzn.to/45Plnv6</t>
+  </si>
+  <si>
+    <t>https://amzn.to/45QLG45</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4xqwYwK</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4fUg8zb</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4xrrkud</t>
+  </si>
+  <si>
+    <t>已通过</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>已添加专属链接</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Humble Bundle</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cross-platform</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assassin's Creed Shadows</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/search?query=Assassin%27s%20Creed%20Shadows</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Green Man Gaming</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Avatar: Frontiers of Pandora</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/avatar-frontiers-of-pandora-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/bayonetta-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Astor: Blade of the Monolith</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/astor-blade-of-the-monolith-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Bayonetta </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Black Myth: Wukong</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/black-myth-wukong-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/call-of-duty-modern-warfare-standard-edition-xbox/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CALL OF DUTY®: MODERN WARFARE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cyberpunk 2077</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/cyberpunk-2077-xbox/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demon Slayer -Kimetsu no Yaiba</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/demon-slayer-kimetsu-no-yaiba-the-hinokami-chronicles-2-deluxe-edition-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Elden Ring</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/elden-ring-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Final Fantasy VII Rebirth</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/final-fantasy-vii-rebirth-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Final Fantasy XVI</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/final-fantasy-xvi-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Star Fire: Eternal Cycle</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>steam</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/star-fire-eternal-cycle-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Forza Horizon 5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/forza-horizon-5-xbox/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Metal Gear Solid V: The Definitive Experience</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/metal-gear-solid-v-the-definitive-experience/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ghost of Tsushima</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/ghost-of-tsushima-directors-cut-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>God of War Ragnarök</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/god-of-war-ragnarok-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Witchspire</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/witchspire-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Grand Theft Auto V Enhanced &amp; Great White Shark Card Bundle</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/grand-theft-auto-v-enhanced-great-white-shark-card-bundle-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>Halo Infinite</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/halo-infinite</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/search?query=Halo%20Infinite</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Helldivers 2</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/helldivers-2</t>
-  </si>
-  <si>
-    <t>Hi-Fi Rush</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/hi-fi-rush</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/helldivers-2-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>LEGO® Batman™: Legacy of the Dark Knight</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/lego-batman-legacy-of-the-dark-knight-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Horizon Forbidden West</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/horizon-forbidden-west</t>
-  </si>
-  <si>
-    <t>Hyrule Warriors: Age of Calamity</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/hyrule-warriors-age-of-calamity</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/horizon-forbidden-west-complete-edition-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/the-adventures-of-elliot-the-millennium-tales-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>he Adventures of Elliot: The Millennium Tales</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Indiana Jones and the Great Circle</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/indiana-jones-and-the-great-circle-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Kingdom Come: Deliverance II</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/kingdom-come-deliverance-2</t>
-  </si>
-  <si>
-    <t>Kirby and the Forgotten Land</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/kirby-and-the-forgotten-land</t>
-  </si>
-  <si>
-    <t>Luigi's Mansion 3</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/luigis-mansion-3</t>
-  </si>
-  <si>
-    <t>Mario + Rabbids Sparks of Hope</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/mario-rabbids-sparks-of-hope</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/kingdom-come-deliverance-ii-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MARVEL Tōkon: Fighting Souls Ultimate Edition</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/marvel-tokon-fighting-souls-ultimate-edition-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Destiny 2: Renegades</t>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/destiny-2-renegades-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Destiny 2: The Collection</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/destiny-2-the-collection-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Marvel's Spider-Man 2</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/marvels-spider-man-2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fanatical</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.fanatical.com/en/game/dying-light-2-stay-human</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dying Light 2 Stay Human: Reloaded Edition</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/marvels-spider-man-2-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Marvel's Spider-Man: Miles Morales</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/spider-man-miles-morales</t>
-  </si>
-  <si>
-    <t>Microsoft Flight Simulator</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/microsoft-flight-simulator</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/marvels-spider-man-miles-morales-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Destiny 2: The Edge of Fate</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/destiny-2-the-edge-of-fate-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Monster Hunter Wilds</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/monster-hunter-wilds</t>
-  </si>
-  <si>
-    <t>Pikmin 4</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/pikmin-4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/monster-hunter-wilds-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>007 First Light</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/007-first-light-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Ratchet &amp; Clank: Rift Apart</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/ratchet-and-clank-rift-apart</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/search?query=Ratchet%20Clank%20Rift%20Apart</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Red Dead Redemption 2</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/red-dead-redemption-2</t>
-  </si>
-  <si>
-    <t>Returnal</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/returnal</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/red-dead-redemption-2-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/returnal-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Rise of the Ronin</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/rise-of-the-ronin</t>
-  </si>
-  <si>
-    <t>Sea of Thieves</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/sea-of-thieves</t>
-  </si>
-  <si>
-    <t>Silent Hill 2 Remake</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/silent-hill-2-remake</t>
-  </si>
-  <si>
-    <t>Splatoon 3</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/splatoon-3</t>
-  </si>
-  <si>
-    <t>Star Wars Outlaws</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/star-wars-outlaws</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/rise-of-the-ronin-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sea of Thieves Castaway’s Ancient Coin Pack – 550 Coins</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/sea-of-thieves-castaways-ancient-coin-pack-550-coins-xbox/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SILENT HILL: Townfall</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/silent-hill-townfall-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/sovereign-tower-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sovereign Tower</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/star-wars-outlaws-gold-edition-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>STAR WARS: OUTLAWS – Gold Edition</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Starfield</t>
-  </si>
-  <si>
-    <t>new-release, longtail</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/starfield</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/starfield-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Stellar Blade</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/stellar-blade</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/stellar-blade-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>The Last of Us Part II Remastered</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/the-last-of-us-part-ii-remastered</t>
-  </si>
-  <si>
-    <t>Xenoblade Chronicles 3</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/xenoblade-chronicles-3</t>
-  </si>
-  <si>
-    <t>Baldur's Gate 3</t>
-  </si>
-  <si>
-    <t>https://www.humblebundle.com/store/baldurs-gate-3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/the-last-of-us-part-ii-remastered-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Disney Dreamlight Valley</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.greenmangaming.com/games/disney-dreamlight-valley-pc/</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Baldur's Gate II: Enhanced Edition</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.humblebundle.com/store/baldurs-gate-ii-enhanced-edition?hmb_source=search_bar</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>EA Sports FC 25</t>
-  </si>
-  <si>
-    <t>https://www.humblebundle.com/store/ea-sports-fc-25</t>
-  </si>
-  <si>
-    <t>Dying Light 2</t>
-  </si>
-  <si>
-    <t>https://www.fanatical.com/en/game/dying-light-2-stay-human</t>
-  </si>
-  <si>
-    <t>Hogwarts Legacy</t>
-  </si>
-  <si>
-    <t>https://www.fanatical.com/en/game/hogwarts-legacy</t>
-  </si>
-  <si>
-    <t>怎么用这张表</t>
-  </si>
-  <si>
-    <t>1) 先看【①联盟申请清单】 sheet，按里面网址去申请 4 个联盟账号。</t>
-  </si>
-  <si>
-    <t>2) 申请通过后，点开本表『当前商品链接（具体商品页）』列里那行对应的链接，在网站里找到这个商品，用你的联盟后台生成『带你追踪ID的推广链接』。</t>
-  </si>
-  <si>
-    <t>3) 回到【②游戏链接填报表】，在黄底列『【请回填】联盟推广链接』粘贴该链接；『回填状态』写『已填』。</t>
-  </si>
-  <si>
-    <t>4) 不用每个都填：先填你已通过的那几家网站对应的行即可，其余留空。</t>
-  </si>
-  <si>
-    <t>5) 填完后把整个 .xlsx 文件发回给我，我会把链接写进网站（更新 deals.json 的 storeUrl，并按需打开 config.ts 里对应网络的 enabled）。</t>
-  </si>
-  <si>
-    <t>关于『链接状态』列：</t>
-  </si>
-  <si>
-    <t>- 『已核实』：商品页 URL 已逐个联网核实，点开就是正确商品，直接用它生成联盟链接即可。</t>
-  </si>
-  <si>
-    <t>- 『推测·请确认』（橙色单元格）：GMG（被反爬保护，无法自动核实）和 Humble（官方商品页未搜到）这两家给的是『按命名规律推测的链接』，点开若是 404 或跳首页，请在该网站搜索框里搜游戏名，用你搜到的真实商品页生成联盟链接。</t>
-  </si>
-  <si>
-    <t>注意事项：</t>
-  </si>
-  <si>
-    <t>- 亚马逊：别手标价格、别用短链（bit.ly等）、文章页必须有 FTC 声明（网站模板已内置）。</t>
-  </si>
-  <si>
-    <t>- 一个游戏当前只挂了一个网站（见『网站/联盟』列），所以每行只需填那一家对应的推广链接。</t>
-  </si>
-  <si>
-    <t>- 若你某游戏想同时挂多家（比如 GMG + Humble），告诉我，我可以把那行拆成多行。</t>
-  </si>
-  <si>
-    <t>- 推广链接必须是『带你自己联盟ID』的完整链接，否则佣金不算你的。</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4wNJW7Q</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4q2cHLd</t>
-  </si>
-  <si>
-    <t>https://amzn.to/3RRsVdI</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4pZh1et</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4hjNmdI</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4fRrp33</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4bxrRCl</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4wUHyft</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4q4oucf</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4z1cmfZ</t>
-  </si>
-  <si>
-    <t>https://amzn.to/45Plnv6</t>
-  </si>
-  <si>
-    <t>https://amzn.to/45QLG45</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4xqwYwK</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4fUg8zb</t>
-  </si>
-  <si>
-    <t>https://amzn.to/4xrrkud</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/indiana-jones-great-circle</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>已通过</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>已添加专属链接</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Humble Bundle</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cross-platform</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assassin's Creed Shadows</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/search?query=Assassin%27s%20Creed%20Shadows</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Green Man Gaming</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Avatar: Frontiers of Pandora</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/avatar-frontiers-of-pandora-pc/</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/bayonetta-pc/</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Astor: Blade of the Monolith</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/astor-blade-of-the-monolith-pc/</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Bayonetta </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Black Myth: Wukong</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/black-myth-wukong-pc/</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/call-of-duty-modern-warfare-standard-edition-xbox/</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>CALL OF DUTY®: MODERN WARFARE</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cyberpunk 2077</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/cyberpunk-2077-xbox/</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Demon Slayer -Kimetsu no Yaiba</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/demon-slayer-kimetsu-no-yaiba-the-hinokami-chronicles-2-deluxe-edition-pc/</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Elden Ring</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/elden-ring-pc/</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Final Fantasy VII Rebirth</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/final-fantasy-vii-rebirth-pc/</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Final Fantasy XVI</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/final-fantasy-xvi-pc/</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Star Fire: Eternal Cycle</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>steam</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/star-fire-eternal-cycle-pc/</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Forza Horizon 5</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/forza-horizon-5-xbox/</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Metal Gear Solid V: The Definitive Experience</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/metal-gear-solid-v-the-definitive-experience/</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ghost of Tsushima</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/ghost-of-tsushima-directors-cut-pc/</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>God of War Ragnarök</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/god-of-war-ragnarok-pc/</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Witchspire</t>
-  </si>
-  <si>
-    <t>https://www.greenmangaming.com/games/witchspire-pc/</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Grand Theft Auto V Enhanced &amp; Great White Shark Card Bundle</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.humblebundle.com/store/ea-sports-fc-25-ultimate-edition-switch?hmb_source=search_bar</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1206,10 +1301,10 @@
         <v>12</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>178</v>
+        <v>129</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>179</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="27" x14ac:dyDescent="0.15">
@@ -1237,7 +1332,7 @@
     </row>
     <row r="6" spans="1:7" ht="27" x14ac:dyDescent="0.15">
       <c r="A6" s="3" t="s">
-        <v>180</v>
+        <v>131</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>21</v>
@@ -1370,7 +1465,7 @@
         <v>45</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>162</v>
+        <v>114</v>
       </c>
       <c r="I4" s="4"/>
     </row>
@@ -1397,7 +1492,7 @@
         <v>45</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>163</v>
+        <v>115</v>
       </c>
       <c r="I5" s="4"/>
     </row>
@@ -1424,7 +1519,7 @@
         <v>45</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>164</v>
+        <v>116</v>
       </c>
       <c r="I6" s="4"/>
     </row>
@@ -1451,7 +1546,7 @@
         <v>45</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>165</v>
+        <v>117</v>
       </c>
       <c r="I7" s="4"/>
     </row>
@@ -1478,7 +1573,7 @@
         <v>45</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>166</v>
+        <v>118</v>
       </c>
       <c r="I8" s="4"/>
     </row>
@@ -1505,7 +1600,7 @@
         <v>45</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>167</v>
+        <v>119</v>
       </c>
       <c r="I9" s="4"/>
     </row>
@@ -1532,7 +1627,7 @@
         <v>45</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>168</v>
+        <v>120</v>
       </c>
       <c r="I10" s="4"/>
     </row>
@@ -1559,7 +1654,7 @@
         <v>45</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>169</v>
+        <v>121</v>
       </c>
       <c r="I11" s="4"/>
     </row>
@@ -1586,7 +1681,7 @@
         <v>45</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>170</v>
+        <v>122</v>
       </c>
       <c r="I12" s="4"/>
     </row>
@@ -1613,7 +1708,7 @@
         <v>45</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>171</v>
+        <v>123</v>
       </c>
       <c r="I13" s="4"/>
     </row>
@@ -1640,7 +1735,7 @@
         <v>45</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>172</v>
+        <v>124</v>
       </c>
       <c r="I14" s="4"/>
     </row>
@@ -1667,7 +1762,7 @@
         <v>45</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>173</v>
+        <v>125</v>
       </c>
       <c r="I15" s="4"/>
     </row>
@@ -1694,7 +1789,7 @@
         <v>45</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>174</v>
+        <v>126</v>
       </c>
       <c r="I16" s="4"/>
     </row>
@@ -1721,7 +1816,7 @@
         <v>45</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>175</v>
+        <v>127</v>
       </c>
       <c r="I17" s="4"/>
     </row>
@@ -1748,7 +1843,7 @@
         <v>45</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>176</v>
+        <v>128</v>
       </c>
       <c r="I18" s="4"/>
     </row>
@@ -1757,13 +1852,13 @@
         <v>16</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>184</v>
+        <v>135</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>182</v>
+        <v>133</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>181</v>
+        <v>132</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>48</v>
@@ -1773,7 +1868,7 @@
         <v>80</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>183</v>
+        <v>134</v>
       </c>
       <c r="I19" s="4"/>
     </row>
@@ -1785,7 +1880,7 @@
         <v>14</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>81</v>
@@ -1798,7 +1893,7 @@
         <v>80</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>189</v>
+        <v>140</v>
       </c>
       <c r="I20" s="4"/>
     </row>
@@ -1810,7 +1905,7 @@
         <v>14</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>185</v>
+        <v>136</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>79</v>
@@ -1823,7 +1918,7 @@
         <v>80</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>186</v>
+        <v>137</v>
       </c>
       <c r="I21" s="4"/>
     </row>
@@ -1835,7 +1930,7 @@
         <v>14</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>190</v>
+        <v>141</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>42</v>
@@ -1848,7 +1943,7 @@
         <v>80</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>187</v>
+        <v>138</v>
       </c>
       <c r="I22" s="4"/>
     </row>
@@ -1860,7 +1955,7 @@
         <v>14</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>191</v>
+        <v>142</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>81</v>
@@ -1873,7 +1968,7 @@
         <v>80</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>192</v>
+        <v>143</v>
       </c>
       <c r="I23" s="4"/>
     </row>
@@ -1885,7 +1980,7 @@
         <v>14</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>194</v>
+        <v>145</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>85</v>
@@ -1898,7 +1993,7 @@
         <v>80</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>193</v>
+        <v>144</v>
       </c>
       <c r="I24" s="4"/>
     </row>
@@ -1910,7 +2005,7 @@
         <v>14</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>195</v>
+        <v>146</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>85</v>
@@ -1923,7 +2018,7 @@
         <v>80</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>196</v>
+        <v>147</v>
       </c>
       <c r="I25" s="4"/>
     </row>
@@ -1932,10 +2027,10 @@
         <v>23</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>184</v>
+        <v>135</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>197</v>
+        <v>148</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="3" t="s">
@@ -1946,7 +2041,7 @@
         <v>80</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>198</v>
+        <v>149</v>
       </c>
       <c r="I26" s="4"/>
     </row>
@@ -1958,7 +2053,7 @@
         <v>14</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>79</v>
@@ -1971,7 +2066,7 @@
         <v>80</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>200</v>
+        <v>151</v>
       </c>
       <c r="I27" s="4"/>
     </row>
@@ -1983,7 +2078,7 @@
         <v>14</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>201</v>
+        <v>152</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>81</v>
@@ -1996,7 +2091,7 @@
         <v>80</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>202</v>
+        <v>153</v>
       </c>
       <c r="I28" s="4"/>
     </row>
@@ -2008,7 +2103,7 @@
         <v>14</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>203</v>
+        <v>154</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>81</v>
@@ -2021,7 +2116,7 @@
         <v>80</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>204</v>
+        <v>155</v>
       </c>
       <c r="I29" s="4"/>
     </row>
@@ -2033,10 +2128,10 @@
         <v>14</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>205</v>
+        <v>156</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>206</v>
+        <v>157</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
@@ -2044,7 +2139,7 @@
         <v>80</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>207</v>
+        <v>158</v>
       </c>
       <c r="I30" s="4"/>
     </row>
@@ -2056,7 +2151,7 @@
         <v>14</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>208</v>
+        <v>159</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>85</v>
@@ -2069,7 +2164,7 @@
         <v>80</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>209</v>
+        <v>160</v>
       </c>
       <c r="I31" s="4"/>
     </row>
@@ -2081,10 +2176,10 @@
         <v>14</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>210</v>
+        <v>161</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>206</v>
+        <v>157</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
@@ -2092,7 +2187,7 @@
         <v>80</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>211</v>
+        <v>162</v>
       </c>
       <c r="I32" s="4"/>
     </row>
@@ -2104,7 +2199,7 @@
         <v>14</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>212</v>
+        <v>163</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>81</v>
@@ -2117,7 +2212,7 @@
         <v>80</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>213</v>
+        <v>164</v>
       </c>
       <c r="I33" s="4"/>
     </row>
@@ -2129,7 +2224,7 @@
         <v>14</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>81</v>
@@ -2142,7 +2237,7 @@
         <v>80</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>215</v>
+        <v>166</v>
       </c>
       <c r="I34" s="4"/>
     </row>
@@ -2154,7 +2249,7 @@
         <v>14</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>216</v>
+        <v>167</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="3"/>
@@ -2163,7 +2258,7 @@
         <v>80</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>217</v>
+        <v>168</v>
       </c>
       <c r="I35" s="4"/>
     </row>
@@ -2175,7 +2270,7 @@
         <v>14</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>218</v>
+        <v>169</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="3"/>
@@ -2183,7 +2278,9 @@
       <c r="G36" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H36" s="5"/>
+      <c r="H36" s="5" t="s">
+        <v>170</v>
+      </c>
       <c r="I36" s="4"/>
     </row>
     <row r="37" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -2194,7 +2291,7 @@
         <v>14</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>86</v>
+        <v>171</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>85</v>
@@ -2202,13 +2299,13 @@
       <c r="E37" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F37" s="3" t="s">
-        <v>87</v>
-      </c>
+      <c r="F37" s="3"/>
       <c r="G37" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H37" s="5"/>
+      <c r="H37" s="8" t="s">
+        <v>172</v>
+      </c>
       <c r="I37" s="4"/>
     </row>
     <row r="38" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -2219,7 +2316,7 @@
         <v>14</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>88</v>
+        <v>173</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>81</v>
@@ -2227,16 +2324,16 @@
       <c r="E38" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F38" s="3" t="s">
-        <v>89</v>
-      </c>
+      <c r="F38" s="3"/>
       <c r="G38" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H38" s="5"/>
+      <c r="H38" s="5" t="s">
+        <v>174</v>
+      </c>
       <c r="I38" s="4"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A39" s="4">
         <v>36</v>
       </c>
@@ -2244,21 +2341,17 @@
         <v>14</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>91</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="D39" s="4"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
       <c r="G39" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H39" s="5"/>
+      <c r="H39" s="5" t="s">
+        <v>176</v>
+      </c>
       <c r="I39" s="4"/>
     </row>
     <row r="40" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -2269,7 +2362,7 @@
         <v>14</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>92</v>
+        <v>177</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>81</v>
@@ -2277,13 +2370,13 @@
       <c r="E40" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F40" s="3" t="s">
-        <v>93</v>
-      </c>
+      <c r="F40" s="3"/>
       <c r="G40" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H40" s="5"/>
+      <c r="H40" s="5" t="s">
+        <v>178</v>
+      </c>
       <c r="I40" s="4"/>
     </row>
     <row r="41" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -2294,7 +2387,7 @@
         <v>14</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>94</v>
+        <v>180</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>42</v>
@@ -2302,13 +2395,13 @@
       <c r="E41" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>95</v>
-      </c>
+      <c r="F41" s="3"/>
       <c r="G41" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H41" s="5"/>
+      <c r="H41" s="5" t="s">
+        <v>179</v>
+      </c>
       <c r="I41" s="4"/>
     </row>
     <row r="42" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -2319,7 +2412,7 @@
         <v>14</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>85</v>
@@ -2327,13 +2420,13 @@
       <c r="E42" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>177</v>
-      </c>
+      <c r="F42" s="3"/>
       <c r="G42" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H42" s="5"/>
+      <c r="H42" s="5" t="s">
+        <v>182</v>
+      </c>
       <c r="I42" s="4"/>
     </row>
     <row r="43" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -2344,7 +2437,7 @@
         <v>14</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>97</v>
+        <v>183</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>79</v>
@@ -2352,13 +2445,13 @@
       <c r="E43" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>98</v>
-      </c>
+      <c r="F43" s="3"/>
       <c r="G43" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H43" s="5"/>
+      <c r="H43" s="5" t="s">
+        <v>184</v>
+      </c>
       <c r="I43" s="4"/>
     </row>
     <row r="44" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -2369,21 +2462,17 @@
         <v>14</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>100</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="D44" s="4"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
       <c r="G44" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H44" s="5"/>
+      <c r="H44" s="5" t="s">
+        <v>186</v>
+      </c>
       <c r="I44" s="4"/>
     </row>
     <row r="45" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -2394,21 +2483,17 @@
         <v>14</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>102</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="D45" s="4"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
       <c r="G45" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H45" s="5"/>
+      <c r="H45" s="5" t="s">
+        <v>188</v>
+      </c>
       <c r="I45" s="4"/>
     </row>
     <row r="46" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -2419,21 +2504,17 @@
         <v>14</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>104</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="D46" s="4"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
       <c r="G46" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H46" s="5"/>
+      <c r="H46" s="5" t="s">
+        <v>190</v>
+      </c>
       <c r="I46" s="4"/>
     </row>
     <row r="47" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -2444,21 +2525,17 @@
         <v>14</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>106</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="D47" s="4"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
       <c r="G47" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H47" s="5"/>
+      <c r="H47" s="5" t="s">
+        <v>195</v>
+      </c>
       <c r="I47" s="4"/>
     </row>
     <row r="48" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -2469,7 +2546,7 @@
         <v>14</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>81</v>
@@ -2477,13 +2554,13 @@
       <c r="E48" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>108</v>
-      </c>
+      <c r="F48" s="3"/>
       <c r="G48" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H48" s="5"/>
+      <c r="H48" s="5" t="s">
+        <v>197</v>
+      </c>
       <c r="I48" s="4"/>
     </row>
     <row r="49" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -2494,21 +2571,17 @@
         <v>14</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>110</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="D49" s="4"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
       <c r="G49" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H49" s="5"/>
+      <c r="H49" s="5" t="s">
+        <v>199</v>
+      </c>
       <c r="I49" s="4"/>
     </row>
     <row r="50" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -2519,7 +2592,7 @@
         <v>14</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>111</v>
+        <v>200</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>79</v>
@@ -2527,16 +2600,16 @@
       <c r="E50" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="F50" s="3" t="s">
-        <v>112</v>
-      </c>
+      <c r="F50" s="3"/>
       <c r="G50" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H50" s="5"/>
+      <c r="H50" s="5" t="s">
+        <v>201</v>
+      </c>
       <c r="I50" s="4"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A51" s="4">
         <v>48</v>
       </c>
@@ -2544,21 +2617,17 @@
         <v>14</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>114</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
       <c r="G51" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H51" s="5"/>
+      <c r="H51" s="5" t="s">
+        <v>203</v>
+      </c>
       <c r="I51" s="4"/>
     </row>
     <row r="52" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -2569,7 +2638,7 @@
         <v>14</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>115</v>
+        <v>204</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>81</v>
@@ -2577,13 +2646,13 @@
       <c r="E52" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>116</v>
-      </c>
+      <c r="F52" s="3"/>
       <c r="G52" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H52" s="5"/>
+      <c r="H52" s="5" t="s">
+        <v>205</v>
+      </c>
       <c r="I52" s="4"/>
     </row>
     <row r="53" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -2594,7 +2663,7 @@
         <v>14</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>117</v>
+        <v>206</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>79</v>
@@ -2602,13 +2671,13 @@
       <c r="E53" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="F53" s="3" t="s">
-        <v>118</v>
-      </c>
+      <c r="F53" s="3"/>
       <c r="G53" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H53" s="5"/>
+      <c r="H53" s="5" t="s">
+        <v>207</v>
+      </c>
       <c r="I53" s="4"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.15">
@@ -2619,7 +2688,7 @@
         <v>14</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>81</v>
@@ -2628,12 +2697,14 @@
         <v>57</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H54" s="5"/>
+      <c r="H54" s="5" t="s">
+        <v>208</v>
+      </c>
       <c r="I54" s="4"/>
     </row>
     <row r="55" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -2644,7 +2715,7 @@
         <v>14</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>121</v>
+        <v>209</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>81</v>
@@ -2653,15 +2724,17 @@
         <v>48</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H55" s="5"/>
+      <c r="H55" s="5" t="s">
+        <v>210</v>
+      </c>
       <c r="I55" s="4"/>
     </row>
-    <row r="56" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A56" s="4">
         <v>53</v>
       </c>
@@ -2669,7 +2742,7 @@
         <v>14</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>123</v>
+        <v>211</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>85</v>
@@ -2678,12 +2751,14 @@
         <v>57</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H56" s="5"/>
+      <c r="H56" s="5" t="s">
+        <v>212</v>
+      </c>
       <c r="I56" s="4"/>
     </row>
     <row r="57" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -2694,24 +2769,20 @@
         <v>14</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>126</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="D57" s="4"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
       <c r="G57" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H57" s="5"/>
+      <c r="H57" s="5" t="s">
+        <v>214</v>
+      </c>
       <c r="I57" s="4"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A58" s="4">
         <v>55</v>
       </c>
@@ -2719,21 +2790,17 @@
         <v>14</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>128</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="D58" s="4"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
       <c r="G58" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H58" s="5"/>
+      <c r="H58" s="5" t="s">
+        <v>215</v>
+      </c>
       <c r="I58" s="4"/>
     </row>
     <row r="59" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -2744,7 +2811,7 @@
         <v>14</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>129</v>
+        <v>218</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>79</v>
@@ -2753,15 +2820,17 @@
         <v>48</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="G59" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H59" s="5"/>
+      <c r="H59" s="5" t="s">
+        <v>217</v>
+      </c>
       <c r="I59" s="4"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A60" s="4">
         <v>57</v>
       </c>
@@ -2769,21 +2838,23 @@
         <v>14</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>131</v>
+        <v>219</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>85</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>132</v>
+        <v>91</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>133</v>
+        <v>92</v>
       </c>
       <c r="G60" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H60" s="5"/>
+      <c r="H60" s="5" t="s">
+        <v>220</v>
+      </c>
       <c r="I60" s="4"/>
     </row>
     <row r="61" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -2794,7 +2865,7 @@
         <v>14</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>134</v>
+        <v>221</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>81</v>
@@ -2803,12 +2874,14 @@
         <v>48</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>135</v>
+        <v>93</v>
       </c>
       <c r="G61" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H61" s="5"/>
+      <c r="H61" s="5" t="s">
+        <v>222</v>
+      </c>
       <c r="I61" s="4"/>
     </row>
     <row r="62" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -2819,7 +2892,7 @@
         <v>14</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>136</v>
+        <v>223</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>81</v>
@@ -2828,12 +2901,14 @@
         <v>43</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="G62" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H62" s="5"/>
+      <c r="H62" s="5" t="s">
+        <v>224</v>
+      </c>
       <c r="I62" s="4"/>
     </row>
     <row r="63" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -2844,7 +2919,7 @@
         <v>14</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>138</v>
+        <v>225</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>42</v>
@@ -2853,23 +2928,25 @@
         <v>57</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="G63" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H63" s="5"/>
+      <c r="H63" s="5" t="s">
+        <v>226</v>
+      </c>
       <c r="I63" s="4"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A64" s="4">
         <v>61</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>20</v>
+        <v>131</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>140</v>
+        <v>227</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>79</v>
@@ -2878,12 +2955,14 @@
         <v>51</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="G64" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H64" s="5"/>
+      <c r="H64" s="5" t="s">
+        <v>228</v>
+      </c>
       <c r="I64" s="4"/>
     </row>
     <row r="65" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -2894,7 +2973,7 @@
         <v>20</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>142</v>
+        <v>229</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>79</v>
@@ -2903,12 +2982,14 @@
         <v>51</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>143</v>
+        <v>97</v>
       </c>
       <c r="G65" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H65" s="5"/>
+      <c r="H65" s="5" t="s">
+        <v>230</v>
+      </c>
       <c r="I65" s="4"/>
     </row>
     <row r="66" spans="1:9" ht="27" x14ac:dyDescent="0.15">
@@ -2916,10 +2997,10 @@
         <v>63</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>144</v>
+        <v>194</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>79</v>
@@ -2928,12 +3009,14 @@
         <v>57</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>145</v>
+        <v>193</v>
       </c>
       <c r="G66" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="H66" s="5"/>
+      <c r="H66" s="3" t="s">
+        <v>193</v>
+      </c>
       <c r="I66" s="4"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.15">
@@ -2944,7 +3027,7 @@
         <v>26</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>146</v>
+        <v>98</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>79</v>
@@ -2953,12 +3036,14 @@
         <v>51</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>147</v>
+        <v>99</v>
       </c>
       <c r="G67" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="H67" s="5"/>
+      <c r="H67" s="3" t="s">
+        <v>99</v>
+      </c>
       <c r="I67" s="4"/>
     </row>
   </sheetData>
@@ -2969,9 +3054,10 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="H19" r:id="rId1" xr:uid="{02F8BF2D-5194-4074-AB9D-0555A539C933}"/>
+    <hyperlink ref="H37" r:id="rId2" xr:uid="{C09A986B-AD7D-4C10-BCB2-FD37A6E3BF74}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -2985,7 +3071,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.15">
@@ -2993,27 +3079,27 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" s="7" t="s">
-        <v>149</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="27" x14ac:dyDescent="0.15">
       <c r="A4" s="7" t="s">
-        <v>150</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A5" s="7" t="s">
-        <v>151</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A6" s="7" t="s">
-        <v>152</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="27" x14ac:dyDescent="0.15">
       <c r="A7" s="7" t="s">
-        <v>153</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.15">
@@ -3021,17 +3107,17 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A9" s="7" t="s">
-        <v>154</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A10" s="7" t="s">
-        <v>155</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A11" s="7" t="s">
-        <v>156</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.15">
@@ -3039,27 +3125,27 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A13" s="7" t="s">
-        <v>157</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A14" s="7" t="s">
-        <v>158</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A15" s="7" t="s">
-        <v>159</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A16" s="7" t="s">
-        <v>160</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A17" s="7" t="s">
-        <v>161</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
